--- a/resources/templates/Checklist_Positions/Template_ASP2.xlsx
+++ b/resources/templates/Checklist_Positions/Template_ASP2.xlsx
@@ -1029,7 +1029,7 @@
     <t>Recommended:</t>
   </si>
   <si>
-    <t>NORITA C. VASQUEZ</t>
+    <t>${encoder_name}</t>
   </si>
   <si>
     <t>RONALD KEVIN C. DEL ROSARIO</t>
@@ -1038,7 +1038,7 @@
     <t>VERNA C. CABAYA</t>
   </si>
   <si>
-    <t>Administrative Assistant III</t>
+    <t>${user_position}</t>
   </si>
   <si>
     <t>Administrative Officer IV-HR</t>
@@ -1047,7 +1047,7 @@
     <t>Administrative Officer V</t>
   </si>
   <si>
-    <t xml:space="preserve">Date:  </t>
+    <t>Date: ${date_of_signing}</t>
   </si>
   <si>
     <t>APC Form - (Revised 2018)</t>
@@ -1411,7 +1411,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <i/>
       <sz val="8.5"/>
       <color rgb="FFFF0000"/>
@@ -1428,6 +1427,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <i/>
       <sz val="8.5"/>
       <color rgb="FFFF0000"/>
@@ -3194,22 +3194,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
